--- a/docs/Score_Card_Calculation_Proposed.xlsx
+++ b/docs/Score_Card_Calculation_Proposed.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{3FB8EE00-BF17-4987-9D4F-36973ABFA87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A624A3-036D-49C6-9AB8-2CE0FF518346}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{0219637B-15DE-4829-A5A4-F607DC33C03F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0219637B-15DE-4829-A5A4-F607DC33C03F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Scorecard_Calculation" sheetId="1" r:id="rId1"/>

--- a/docs/Score_Card_Calculation_Proposed.xlsx
+++ b/docs/Score_Card_Calculation_Proposed.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{3FB8EE00-BF17-4987-9D4F-36973ABFA87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A624A3-036D-49C6-9AB8-2CE0FF518346}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0219637B-15DE-4829-A5A4-F607DC33C03F}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="1" xr2:uid="{0219637B-15DE-4829-A5A4-F607DC33C03F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Scorecard_Calculation" sheetId="1" r:id="rId1"/>
@@ -498,6 +498,84 @@
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -507,109 +585,31 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -978,660 +978,660 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="14" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10" ht="14" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" s="11" customFormat="1">
-      <c r="A5" s="7" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" s="8" customFormat="1">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>15</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="5">
         <v>15</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <f t="shared" ref="E5:E11" si="0">IFERROR(C5/D5,"")</f>
         <v>1</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" s="11" customFormat="1">
-      <c r="A6" s="7" t="s">
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" s="8" customFormat="1">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="5">
         <v>5</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" s="11" customFormat="1">
-      <c r="A7" s="7" t="s">
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" s="8" customFormat="1">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="5">
         <v>15</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="5">
         <v>15</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" s="11" customFormat="1">
-      <c r="A8" s="7" t="s">
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" s="8" customFormat="1">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
         <v>0</v>
       </c>
-      <c r="D8" s="8">
-        <v>10</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="D8" s="5">
+        <v>10</v>
+      </c>
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" s="11" customFormat="1">
-      <c r="A9" s="7" t="s">
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" s="8" customFormat="1">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="5">
         <v>4</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" s="11" customFormat="1">
-      <c r="A10" s="7" t="s">
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" s="8" customFormat="1">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="5">
         <v>0</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="5">
         <v>15</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" s="11" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" s="8" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="5">
         <v>0</v>
       </c>
-      <c r="D11" s="8">
-        <v>10</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" s="11" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" s="8" customFormat="1">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" s="14" customFormat="1" ht="28">
-      <c r="A15" s="12" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" s="11" customFormat="1" ht="28">
+      <c r="A15" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="5">
         <v>30</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="5">
         <f>SUMIFS($C$5:$C$11,$A$5:$A$11,A16,$F$5:$F$11,"Yes")</f>
         <v>18</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="5">
         <f>SUMIFS($D$5:$D$11,$A$5:$A$11,A16,$F$5:$F$11,"Yes")</f>
         <v>20</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="6">
         <f>IFERROR(C16/D16,"")</f>
         <v>0.9</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="5">
         <f>IF(D16&gt;0,E16*B16,0)</f>
         <v>27</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="5">
         <v>25</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="5">
         <f>SUMIFS($C$5:$C$11,$A$5:$A$11,A17,$F$5:$F$11,"Yes")</f>
         <v>15</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <f>SUMIFS($D$5:$D$11,$A$5:$A$11,A17,$F$5:$F$11,"Yes")</f>
         <v>25</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="6">
         <f>IFERROR(C17/D17,"")</f>
         <v>0.6</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <f>IF(D17&gt;0,E17*B17,0)</f>
         <v>15</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="5">
         <v>25</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="5">
         <f>SUMIFS($C$5:$C$11,$A$5:$A$11,A18,$F$5:$F$11,"Yes")</f>
         <v>4</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="5">
         <f>SUMIFS($D$5:$D$11,$A$5:$A$11,A18,$F$5:$F$11,"Yes")</f>
         <v>20</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="6">
         <f>IFERROR(C18/D18,"")</f>
         <v>0.2</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="5">
         <f>IF(D18&gt;0,E18*B18,0)</f>
         <v>5</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="5">
         <v>20</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="5">
         <f>SUMIFS($C$5:$C$11,$A$5:$A$11,A19,$F$5:$F$11,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="5">
         <f>SUMIFS($D$5:$D$11,$A$5:$A$11,A19,$F$5:$F$11,"Yes")</f>
         <v>10</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="6">
         <f>IFERROR(C19/D19,"")</f>
         <v>0</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="5">
         <f>IF(D19&gt;0,E19*B19,0)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="28">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="15.5">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="5">
         <f>SUM(F16:F19)</f>
         <v>47</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="5">
         <f>SUMIFS(B16:B19,D16:D19,"&gt;0")</f>
         <v>100</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="5">
         <v>100</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="13">
         <f>IFERROR(B25/C25*D25,"")</f>
         <v>47</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="13">
         <f>E25</f>
         <v>47</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="4"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="4"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="A27" s="1"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="29">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10" ht="43.5">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10" ht="29">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10" ht="43.5">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1667,282 +1667,282 @@
   <sheetFormatPr defaultColWidth="26.26953125" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:6" ht="26" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="32">
         <v>40</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="24">
-        <v>10</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="18">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="20">
         <v>5</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="28" t="s">
+      <c r="C4" s="33"/>
+      <c r="D4" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="22">
         <v>15</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="25" t="s">
+      <c r="C5" s="33"/>
+      <c r="D5" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="20">
         <v>5</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="22">
         <v>5</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="35">
         <v>20</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="24">
         <v>5</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="36"/>
+      <c r="D8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="24">
         <v>5</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="33">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="24">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="38">
         <v>20</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="38">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="26">
+        <v>10</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="39"/>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="26">
         <v>5</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="40"/>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="26">
         <v>5</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="41">
         <v>20</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="27">
-        <v>10</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="20">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="42"/>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="20">
         <v>5</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="43"/>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="20">
         <v>5</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="4" t="s">
         <v>80</v>
       </c>
     </row>
